--- a/dist/Apptio_Process_Catalog_L0-L2.xlsx
+++ b/dist/Apptio_Process_Catalog_L0-L2.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L0 Map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Process Catalog L0-L2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E2E Flow Steps" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tool Config Reference" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework Reference" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="L0 Map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Process Catalog L0-L2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="E2E Flow Steps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tool Config Reference" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Framework Reference" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sources" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'L0 Map'!$A$1:$I$1</definedName>

--- a/dist/Apptio_Process_Catalog_L0-L2.xlsx
+++ b/dist/Apptio_Process_Catalog_L0-L2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L0 Map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Process Catalog L0-L2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E2E Flow Steps" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BPMN Diagrams" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tool Config Reference" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework Reference" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Calendar" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changelog" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="L0 Map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Process Catalog L0-L2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="E2E Flow Steps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BPMN Diagrams" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tool Config Reference" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Framework Reference" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Operating Calendar" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Changelog" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'L0 Map'!$A$1:$H$1</definedName>

--- a/dist/Apptio_Process_Catalog_L0-L2.xlsx
+++ b/dist/Apptio_Process_Catalog_L0-L2.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L0 Map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Process Catalog L0-L2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variants" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E2E Flow Steps" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BPMN Diagrams" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tool Config Reference" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework Reference" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Calendar" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changelog" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="L0 Map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Process Catalog L0-L2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Variants" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="E2E Flow Steps" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="BPMN Diagrams" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Tool Config Reference" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Framework Reference" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Operating Calendar" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Changelog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'L0 Map'!$A$1:$H$1</definedName>

--- a/dist/Apptio_Process_Catalog_L0-L2.xlsx
+++ b/dist/Apptio_Process_Catalog_L0-L2.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="L0 Map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Process Catalog L0-L2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Variants" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="E2E Flow Steps" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="BPMN Diagrams" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Tool Config Reference" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Framework Reference" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Operating Calendar" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Changelog" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="L0 Map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Process Catalog L0-L2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variants" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E2E Flow Steps" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BPMN Diagrams" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tool Config Reference" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework Reference" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Calendar" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changelog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'L0 Map'!$A$1:$H$1</definedName>
